--- a/sheets/조재수대금교본/검수/대금 시나위 (3).xlsx
+++ b/sheets/조재수대금교본/검수/대금 시나위 (3).xlsx
@@ -3179,11 +3179,7 @@
     </row>
     <row r="8" ht="79.8" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="23"/>
       <c r="D8" s="21"/>
       <c r="E8" s="23"/>
@@ -3254,12 +3250,7 @@
       <c r="C10" s="24"/>
       <c r="D10" s="21"/>
       <c r="E10" s="24"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="24"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
@@ -3267,12 +3258,7 @@
         </is>
       </c>
       <c r="I10" s="24"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="24"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
@@ -3284,17 +3270,9 @@
       <c r="O10" s="24"/>
       <c r="P10" s="21"/>
       <c r="Q10" s="24"/>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R10" s="21"/>
       <c r="S10" s="24"/>
-      <c r="T10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T10" s="21"/>
       <c r="U10" s="24"/>
     </row>
     <row r="11" ht="79.8" customHeight="true">
@@ -3333,14 +3311,14 @@
       <c r="Q11" s="22"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞c
+          <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
       <c r="S11" s="22"/>
       <c r="T11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅋ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="U11" s="22"/>
@@ -3541,12 +3519,7 @@
     </row>
     <row r="18" ht="79.8" customHeight="true">
       <c r="A18" s="0"/>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="B18" s="21"/>
       <c r="C18" s="24"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
@@ -3556,16 +3529,11 @@
       <c r="E18" s="24"/>
       <c r="F18" s="21"/>
       <c r="G18" s="24"/>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="H18" s="21"/>
       <c r="I18" s="24"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
-‹</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="K18" s="24"/>
@@ -3583,17 +3551,9 @@
         </is>
       </c>
       <c r="Q18" s="24"/>
-      <c r="R18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R18" s="21"/>
       <c r="S18" s="24"/>
-      <c r="T18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T18" s="21"/>
       <c r="U18" s="24"/>
     </row>
     <row r="19" ht="6.0" customHeight="true">
@@ -3773,11 +3733,7 @@
       <c r="Q26" s="23"/>
       <c r="R26" s="21"/>
       <c r="S26" s="23"/>
-      <c r="T26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="T26" s="21"/>
       <c r="U26" s="23"/>
     </row>
     <row r="27" ht="79.8" customHeight="true">
@@ -4007,11 +3963,7 @@
       <c r="Q36" s="24"/>
       <c r="R36" s="21"/>
       <c r="S36" s="24"/>
-      <c r="T36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T36" s="21"/>
       <c r="U36" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/대금 시나위 (3).xlsx
+++ b/sheets/조재수대금교본/검수/대금 시나위 (3).xlsx
@@ -3179,7 +3179,11 @@
     </row>
     <row r="8" ht="79.8" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C8" s="23"/>
       <c r="D8" s="21"/>
       <c r="E8" s="23"/>
@@ -3250,7 +3254,11 @@
       <c r="C10" s="24"/>
       <c r="D10" s="21"/>
       <c r="E10" s="24"/>
-      <c r="F10" s="21"/>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="G10" s="24"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
@@ -3258,7 +3266,11 @@
         </is>
       </c>
       <c r="I10" s="24"/>
-      <c r="J10" s="21"/>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="K10" s="24"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
@@ -3311,14 +3323,14 @@
       <c r="Q11" s="22"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞c
 汰</t>
         </is>
       </c>
       <c r="S11" s="22"/>
       <c r="T11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ㅋ</t>
         </is>
       </c>
       <c r="U11" s="22"/>
@@ -3519,7 +3531,11 @@
     </row>
     <row r="18" ht="79.8" customHeight="true">
       <c r="A18" s="0"/>
-      <c r="B18" s="21"/>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C18" s="24"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
@@ -3529,7 +3545,11 @@
       <c r="E18" s="24"/>
       <c r="F18" s="21"/>
       <c r="G18" s="24"/>
-      <c r="H18" s="21"/>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="I18" s="24"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
@@ -3733,7 +3753,11 @@
       <c r="Q26" s="23"/>
       <c r="R26" s="21"/>
       <c r="S26" s="23"/>
-      <c r="T26" s="21"/>
+      <c r="T26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="U26" s="23"/>
     </row>
     <row r="27" ht="79.8" customHeight="true">

--- a/sheets/조재수대금교본/검수/대금 시나위 (3).xlsx
+++ b/sheets/조재수대금교본/검수/대금 시나위 (3).xlsx
@@ -2920,32 +2920,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="79.8" customHeight="true">
+    <row r="3" ht="89.42" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="79.8" customHeight="true">
+    <row r="4" ht="89.42" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="79.8" customHeight="true">
+    <row r="5" ht="89.42" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="79.8" customHeight="true">
+    <row r="6" ht="89.42" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="79.8" customHeight="true">
+    <row r="7" ht="89.42" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="79.8" customHeight="true">
+    <row r="8" ht="89.42" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="79.8" customHeight="true">
+    <row r="9" ht="89.42" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -3248,7 +3248,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="79.8" customHeight="true">
+    <row r="10" ht="89.42" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -3287,7 +3287,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="79.8" customHeight="true">
+    <row r="11" ht="89.42" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="79.8" customHeight="true">
+    <row r="12" ht="89.42" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -3362,7 +3362,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="79.8" customHeight="true">
+    <row r="13" ht="89.42" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3405,7 +3405,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="79.8" customHeight="true">
+    <row r="14" ht="89.42" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -3444,7 +3444,7 @@
       <c r="T14" s="21"/>
       <c r="U14" s="24"/>
     </row>
-    <row r="15" ht="79.8" customHeight="true">
+    <row r="15" ht="89.42" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -3467,7 +3467,7 @@
       <c r="T15" s="21"/>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="79.8" customHeight="true">
+    <row r="16" ht="89.42" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -3506,7 +3506,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="79.8" customHeight="true">
+    <row r="17" ht="89.42" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -3529,7 +3529,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="23"/>
     </row>
-    <row r="18" ht="79.8" customHeight="true">
+    <row r="18" ht="89.42" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
     <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="71.43" customHeight="true">
+    <row r="20" ht="80.0" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
     </row>
-    <row r="21" ht="79.8" customHeight="true">
+    <row r="21" ht="89.42" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="79.8" customHeight="true">
+    <row r="22" ht="89.42" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="23"/>
@@ -3656,7 +3656,7 @@
       <c r="T22" s="21"/>
       <c r="U22" s="23"/>
     </row>
-    <row r="23" ht="79.8" customHeight="true">
+    <row r="23" ht="89.42" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="23"/>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="U23" s="23"/>
     </row>
-    <row r="24" ht="79.8" customHeight="true">
+    <row r="24" ht="89.42" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="24"/>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="U24" s="24"/>
     </row>
-    <row r="25" ht="79.8" customHeight="true">
+    <row r="25" ht="89.42" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -3733,7 +3733,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="79.8" customHeight="true">
+    <row r="26" ht="89.42" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="23"/>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="79.8" customHeight="true">
+    <row r="27" ht="89.42" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -3783,7 +3783,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="79.8" customHeight="true">
+    <row r="28" ht="89.42" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -3806,7 +3806,7 @@
       <c r="T28" s="21"/>
       <c r="U28" s="24"/>
     </row>
-    <row r="29" ht="79.8" customHeight="true">
+    <row r="29" ht="89.42" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -3829,7 +3829,7 @@
       <c r="T29" s="21"/>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" ht="79.8" customHeight="true">
+    <row r="30" ht="89.42" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="23"/>
@@ -3852,7 +3852,7 @@
       <c r="T30" s="21"/>
       <c r="U30" s="23"/>
     </row>
-    <row r="31" ht="79.8" customHeight="true">
+    <row r="31" ht="89.42" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="23"/>
@@ -3875,7 +3875,7 @@
       <c r="T31" s="21"/>
       <c r="U31" s="23"/>
     </row>
-    <row r="32" ht="79.8" customHeight="true">
+    <row r="32" ht="89.42" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="24"/>
@@ -3898,7 +3898,7 @@
       <c r="T32" s="21"/>
       <c r="U32" s="24"/>
     </row>
-    <row r="33" ht="79.8" customHeight="true">
+    <row r="33" ht="89.42" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -3921,7 +3921,7 @@
       <c r="T33" s="21"/>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="79.8" customHeight="true">
+    <row r="34" ht="89.42" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="23"/>
@@ -3944,7 +3944,7 @@
       <c r="T34" s="21"/>
       <c r="U34" s="23"/>
     </row>
-    <row r="35" ht="79.8" customHeight="true">
+    <row r="35" ht="89.42" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -3967,7 +3967,7 @@
       <c r="T35" s="21"/>
       <c r="U35" s="23"/>
     </row>
-    <row r="36" ht="79.8" customHeight="true">
+    <row r="36" ht="89.42" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="24"/>
@@ -3997,7 +3997,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="18" max="16383" man="1"/>
   </rowBreaks>
